--- a/data/pipeline_data/run_info.xlsx
+++ b/data/pipeline_data/run_info.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,158 @@
         <v>503</v>
       </c>
       <c r="J2" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-10T01:38:13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data\timeseries_wide_SD1.csv</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>900</v>
+      </c>
+      <c r="I3" t="n">
+        <v>503</v>
+      </c>
+      <c r="J3" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:30:10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data\timeseries_wide_SD1.csv</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>123</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>900</v>
+      </c>
+      <c r="I4" t="n">
+        <v>503</v>
+      </c>
+      <c r="J4" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10T03:36:54</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data\timeseries_wide_SD1.csv</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>123</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H5" t="n">
+        <v>900</v>
+      </c>
+      <c r="I5" t="n">
+        <v>503</v>
+      </c>
+      <c r="J5" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-10T12:53:23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data\timeseries_wide_SD1.csv</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>123</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>900</v>
+      </c>
+      <c r="I6" t="n">
+        <v>503</v>
+      </c>
+      <c r="J6" t="n">
         <v>397</v>
       </c>
     </row>
@@ -525,7 +677,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Output: C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data | File: timeseries_wide_SD1.csv | Seed: 123 | Timestamp: 2026-07-06T21:37:32</t>
+          <t>Output: C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data | File: timeseries_wide_SD1.csv | Seed: 123 | Timestamp: 2026-07-10T12:53:23</t>
         </is>
       </c>
     </row>

--- a/data/pipeline_data/run_info.xlsx
+++ b/data/pipeline_data/run_info.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,6 +657,44 @@
         <v>503</v>
       </c>
       <c r="J6" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10T20:08:32</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data\timeseries_wide_SD1.csv</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>123</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>900</v>
+      </c>
+      <c r="I7" t="n">
+        <v>503</v>
+      </c>
+      <c r="J7" t="n">
         <v>397</v>
       </c>
     </row>
@@ -677,7 +715,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Output: C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data | File: timeseries_wide_SD1.csv | Seed: 123 | Timestamp: 2026-07-10T12:53:23</t>
+          <t>Output: C:\Users\prern\Downloads\ThesisFinal\curveql\data\pipeline_data | File: timeseries_wide_SD1.csv | Seed: 123 | Timestamp: 2026-07-10T20:08:32</t>
         </is>
       </c>
     </row>
